--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260611.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260611.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>18.55%</t>
+          <t>18.10%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>4.67%</t>
+          <t>4.82%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>9,760,000</t>
+          <t>9,900,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>4.63%</t>
+          <t>4.72%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>4.59%</t>
+          <t>4.34%</t>
         </is>
       </c>
     </row>
@@ -704,73 +704,73 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.44%</t>
+          <t>4.30%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>4,700,000</t>
+          <t>1,350,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.87%</t>
+          <t>3.90%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>1,350,000</t>
+          <t>12,101,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.86%</t>
+          <t>3.73%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>12,101,000</t>
+          <t>4,700,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.78%</t>
+          <t>3.58%</t>
         </is>
       </c>
     </row>
@@ -792,51 +792,51 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>3.19%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>2,430,000</t>
+          <t>870,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.10%</t>
+          <t>3.00%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>870,000</t>
+          <t>2,430,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.91%</t>
+          <t>2.97%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>2.71%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>2.71%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.19%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.70%</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>5,492,000</t>
+          <t>5,600,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.68%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.51%</t>
         </is>
       </c>
     </row>
@@ -990,51 +990,51 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.33%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>1,520,000</t>
+          <t>16,350,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>16,350,000</t>
+          <t>1,520,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.27%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
@@ -1107,22 +1107,22 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>720,000</t>
+          <t>9,911,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
@@ -1166,29 +1166,29 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>9,911,000</t>
+          <t>690,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
@@ -1232,24 +1232,24 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.71%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>390,000</t>
+          <t>1,497,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>1,497,000</t>
+          <t>390,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.55%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
@@ -1408,46 +1408,46 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>350,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>350,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1474,46 +1474,46 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>900,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.38%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>1,155,000</t>
+          <t>900,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,22 +1525,22 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>5,300,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
@@ -1606,51 +1606,51 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.18%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>450,000</t>
+          <t>340,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.12%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>78,000</t>
+          <t>450,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.08%</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>6,404,084,696</t>
+          <t>5,859,418,494</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>-2,240,533,576</t>
+          <t>-1,955,569,139</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
